--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487157_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487157_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7284</v>
+        <v>4.6287</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6567</v>
+        <v>4.4767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0717</v>
+        <v>0.152</v>
       </c>
       <c r="G2" t="n">
         <v>0.3175</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.045</v>
+        <v>-0.1448</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2492</v>
+        <v>-0.4293</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2042</v>
+        <v>0.2845</v>
       </c>
       <c r="V2" t="n">
         <v>3.6839</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5762</v>
+        <v>3.1843</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0757</v>
+        <v>3.7069</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5004</v>
+        <v>-0.5226</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0459</v>
+        <v>2.324</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5353</v>
+        <v>0.1262</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4895</v>
+        <v>2.1978</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0011</v>
+        <v>3.8721</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0514</v>
+        <v>0.714</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.0503</v>
+        <v>3.1581</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9552</v>
+        <v>-1.5481</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5161</v>
+        <v>-0.5878</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4391</v>
+        <v>-0.9604</v>
       </c>
       <c r="P3" t="n">
         <v>1.158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0881</v>
+        <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>1.944</v>
+        <v>-0.2978</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0048</v>
+        <v>-0.1652</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9392</v>
+        <v>-0.1325</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8839</v>
+        <v>2.726</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6474</v>
+        <v>1.7144</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7635</v>
+        <v>1.0116</v>
       </c>
       <c r="G4" t="n">
-        <v>2.324</v>
+        <v>1.9949</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1262</v>
+        <v>0.0528</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1978</v>
+        <v>1.9421</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8721</v>
+        <v>3.6428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.714</v>
+        <v>1.128</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1581</v>
+        <v>2.5148</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5481</v>
+        <v>-1.6479</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5878</v>
+        <v>-1.0752</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9604</v>
+        <v>-0.5727</v>
       </c>
       <c r="P4" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5982</v>
+        <v>-0.3269</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2247</v>
+        <v>-0.2842</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3735</v>
+        <v>-0.0427</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3661</v>
+        <v>1.9918</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5954</v>
+        <v>0.8929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7706</v>
+        <v>1.0989</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9949</v>
+        <v>1.0459</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0528</v>
+        <v>2.5353</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9421</v>
+        <v>-1.4895</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6428</v>
+        <v>3.0011</v>
       </c>
       <c r="K5" t="n">
-        <v>1.128</v>
+        <v>4.0514</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5148</v>
+        <v>-1.0503</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6479</v>
+        <v>-1.9552</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0752</v>
+        <v>-1.5161</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5727</v>
+        <v>-0.4391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7021</v>
+        <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6868</v>
+        <v>0.3596</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4032</v>
+        <v>-0.1781</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2836</v>
+        <v>0.5377</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2859</v>
+        <v>-0.5717</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6765</v>
+        <v>1.6944</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2488</v>
+        <v>-0.0704</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9254</v>
+        <v>1.7647</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3249</v>
@@ -922,13 +922,13 @@
         <v>3.0881</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1216</v>
+        <v>-0.1038</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7601</v>
+        <v>-0.5816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6385</v>
+        <v>0.4779</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4744</v>
+        <v>-1.3475</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0964</v>
+        <v>0.0038</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.378</v>
+        <v>-1.3513</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3383</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2941</v>
+        <v>-0.1672</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-1.228</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7629</v>
+        <v>-1.3495</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9818</v>
+        <v>-0.6218</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7812</v>
+        <v>-0.7276</v>
       </c>
       <c r="G8" t="n">
         <v>-1.253</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7958</v>
+        <v>-0.3824</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2974</v>
+        <v>0.0625</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4984</v>
+        <v>-0.4449</v>
       </c>
       <c r="V8" t="n">
         <v>0.2859</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9445</v>
+        <v>-1.7849</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3083</v>
+        <v>-0.1487</v>
       </c>
       <c r="F9" t="n">
         <v>-1.6361</v>
@@ -1156,10 +1156,10 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0291</v>
+        <v>0.1887</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>-0.0056</v>
       </c>
       <c r="U9" t="n">
         <v>0.1943</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6745</v>
+        <v>-2.946</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.218</v>
+        <v>0.2397</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4566</v>
+        <v>-3.1856</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1916</v>
+        <v>-1.8749</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9067</v>
+        <v>-0.7254</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2849</v>
+        <v>-1.1496</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1717</v>
+        <v>1.9753</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6262</v>
+        <v>1.3247</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5455</v>
+        <v>0.6505</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0199</v>
+        <v>-3.8502</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2805</v>
+        <v>-2.0501</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2606</v>
+        <v>-1.8001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.772</v>
+        <v>2.8951</v>
       </c>
       <c r="S10" t="n">
-        <v>0.78</v>
+        <v>-0.4607</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9188</v>
+        <v>-0.6861</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1388</v>
+        <v>0.2254</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.0699</v>
+        <v>-2.5404</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0699</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8655</v>
+        <v>-3.7386</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.947</v>
+        <v>-1.8468</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9186</v>
+        <v>-1.8918</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5918</v>
@@ -1312,13 +1312,13 @@
         <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5017</v>
+        <v>-0.3748</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3827</v>
+        <v>-0.3559</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.872</v>
+        <v>-4.5292</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7399</v>
+        <v>-2.0191</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1321</v>
+        <v>-2.5101</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8749</v>
+        <v>-1.1916</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7254</v>
+        <v>-0.9067</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1496</v>
+        <v>-0.2849</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9753</v>
+        <v>-1.1717</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3247</v>
+        <v>-0.6262</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6505</v>
+        <v>-0.5455</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.8502</v>
+        <v>-0.0199</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0501</v>
+        <v>-0.2805</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8001</v>
+        <v>0.2606</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8951</v>
+        <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3868</v>
+        <v>-0.0747</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6657</v>
+        <v>0.1177</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2789</v>
+        <v>-0.1924</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.5404</v>
+        <v>-3.0699</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4559</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.362699999999999</v>
+        <v>-1.470499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.435</v>
+        <v>6.3276</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.798</v>
+        <v>-7.7979</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1341999999999992</v>
+        <v>0.1341999999999997</v>
       </c>
       <c r="H13" t="n">
         <v>-1.8686</v>
@@ -1468,16 +1468,16 @@
         <v>19.3005</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6769</v>
+        <v>-1.7848</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1394</v>
+        <v>-2.247</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4623999999999998</v>
+        <v>0.4624999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.6103</v>
+        <v>-5.610300000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.9709</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.1715</v>
+        <v>10.5508</v>
       </c>
       <c r="E14" t="n">
-        <v>9.375500000000001</v>
+        <v>8.6745</v>
       </c>
       <c r="F14" t="n">
-        <v>1.796</v>
+        <v>1.8763</v>
       </c>
       <c r="G14" t="n">
         <v>6.5317</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4046</v>
+        <v>0.7839</v>
       </c>
       <c r="T14" t="n">
-        <v>1.051</v>
+        <v>0.35</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3536</v>
+        <v>0.4339</v>
       </c>
       <c r="V14" t="n">
         <v>1.8842</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1958</v>
+        <v>3.1695</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4123</v>
+        <v>3.1179</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7836</v>
+        <v>0.0516</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5407</v>
+        <v>-0.0008</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.0573</v>
+        <v>-0.507</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5165</v>
+        <v>0.5062</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3352</v>
+        <v>2.2075</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.8415</v>
+        <v>0.1811</v>
       </c>
       <c r="L15" t="n">
-        <v>5.1767</v>
+        <v>2.0264</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8759</v>
+        <v>-2.2082</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2158</v>
+        <v>-0.6881</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6601</v>
+        <v>-1.5202</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.6672</v>
+        <v>1.3511</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.9833</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8356</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="U15" t="n">
-        <v>2.201</v>
+        <v>0.7158</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5681</v>
+        <v>1.228</v>
       </c>
       <c r="W15" t="n">
-        <v>6.4257</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.337</v>
+        <v>2.5311</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0177</v>
+        <v>2.7113</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3193</v>
+        <v>-0.1801</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0008</v>
+        <v>-0.5407</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.507</v>
+        <v>-4.0573</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5062</v>
+        <v>3.5165</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2075</v>
+        <v>2.3352</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1811</v>
+        <v>-2.8415</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0264</v>
+        <v>5.1767</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2082</v>
+        <v>-2.8759</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6881</v>
+        <v>-1.2158</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5202</v>
+        <v>-1.6601</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.193</v>
+        <v>-5.9833</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7588</v>
+        <v>1.1709</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2247</v>
+        <v>-0.0664</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9835</v>
+        <v>1.2373</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>5.5681</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>6.4257</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3407</v>
+        <v>0.4953</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4645</v>
+        <v>0.1641</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1239</v>
+        <v>0.3312</v>
       </c>
       <c r="G17" t="n">
         <v>4.1063</v>
@@ -1780,13 +1780,13 @@
         <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0945</v>
+        <v>0.2492</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.2145</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0086</v>
+        <v>0.4636</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>G. DARAME PIZARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9033</v>
+        <v>-0.9728</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0226</v>
+        <v>-0.5909</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.3819</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0059</v>
+        <v>-0.7246</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1055</v>
+        <v>0.4492</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9004</v>
+        <v>-1.1738</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5855</v>
+        <v>-0.5648</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0414</v>
+        <v>0.0621</v>
       </c>
       <c r="L18" t="n">
         <v>-0.6269</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4204</v>
+        <v>-0.1598</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1469</v>
+        <v>0.3871</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2735</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9445</v>
+        <v>-0.3411</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6081</v>
+        <v>-0.119</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3364</v>
+        <v>-0.2221</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. DARAME PIZARRO</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0799</v>
+        <v>-1.3911</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5909</v>
+        <v>-0.2778</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.489</v>
+        <v>-1.1133</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7246</v>
+        <v>-1.0059</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4492</v>
+        <v>-0.1055</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1738</v>
+        <v>-0.9004</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5648</v>
+        <v>-0.5855</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0621</v>
+        <v>0.0414</v>
       </c>
       <c r="L19" t="n">
         <v>-0.6269</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1598</v>
+        <v>-0.4204</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3871</v>
+        <v>-0.1469</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.2735</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4482</v>
+        <v>0.4567</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.119</v>
+        <v>0.3077</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3292</v>
+        <v>0.149</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2073</v>
+        <v>-1.8801</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3063</v>
+        <v>-2.0059</v>
       </c>
       <c r="F20" t="n">
-        <v>0.099</v>
+        <v>0.1258</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5884</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3378</v>
+        <v>-0.0106</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.238</v>
+        <v>0.0625</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0998</v>
+        <v>-0.0731</v>
       </c>
       <c r="V20" t="n">
         <v>1.842</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. NDIR</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1558</v>
+        <v>-2.2783</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3034</v>
+        <v>-0.4331</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8525</v>
+        <v>-1.8452</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8257</v>
+        <v>-1.2543</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3134</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5123</v>
+        <v>-0.2577</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1376</v>
+        <v>1.1021</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0155</v>
+        <v>0.5329</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9632</v>
+        <v>-2.3563</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3288</v>
+        <v>-1.5295</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6344</v>
+        <v>-0.8268</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2373</v>
+        <v>-0.3751</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4759</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2386</v>
+        <v>0.195</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>M. NDIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2609</v>
+        <v>-3.0894</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9338</v>
+        <v>-1.1031</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3271</v>
+        <v>-1.9863</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2543</v>
+        <v>-2.8257</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-1.3134</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2577</v>
+        <v>-1.5123</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1021</v>
+        <v>0.1376</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5329</v>
+        <v>0.0155</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.1221</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3563</v>
+        <v>-2.9632</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5295</v>
+        <v>-1.3288</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8268</v>
+        <v>-1.6344</v>
       </c>
       <c r="P22" t="n">
-        <v>0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3577</v>
+        <v>-0.1709</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0708</v>
+        <v>-0.2756</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2869</v>
+        <v>0.1048</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.075</v>
+        <v>-4.7722</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3603</v>
+        <v>-2.459</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7147</v>
+        <v>-2.3132</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8318</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9802</v>
+        <v>0.3226</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7139</v>
+        <v>0.1874</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2664</v>
+        <v>0.1352</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4559</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.362800000000003</v>
+        <v>2.3628</v>
       </c>
       <c r="E24" t="n">
-        <v>7.797899999999998</v>
+        <v>7.798</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.4352</v>
+        <v>-5.4351</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1342000000000003</v>
+        <v>-0.1342000000000008</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8686</v>
+        <v>1.868600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-2.002799999999999</v>
@@ -2302,22 +2302,22 @@
         <v>15.9802</v>
       </c>
       <c r="K24" t="n">
-        <v>8.314900000000002</v>
+        <v>8.3149</v>
       </c>
       <c r="L24" t="n">
-        <v>7.665200000000003</v>
+        <v>7.6652</v>
       </c>
       <c r="M24" t="n">
         <v>-16.1142</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.446399999999999</v>
+        <v>-6.4464</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.667899999999999</v>
+        <v>-9.667899999999998</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.7903</v>
+        <v>-5.790300000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-19.3008</v>
